--- a/KiCAD_Files/FreeDSP_INTEGRA_PANELBOARD/FreeDSP_INTEGRA_PANELBOARD_PartsList.xlsx
+++ b/KiCAD_Files/FreeDSP_INTEGRA_PANELBOARD/FreeDSP_INTEGRA_PANELBOARD_PartsList.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HILO/Documents/KiCad/9.0/projects/FreeDSP_INTEGRA/FreeDSP_INTEGRA_PANELBOARD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2C543851-0838-0C4C-84C3-913F99A852E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C34155-EA58-2A4F-B773-B9E0D21AD2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15000" yWindow="5580" windowWidth="41160" windowHeight="18980" xr2:uid="{5F9E506D-38E0-084A-B434-EE95D9C6630C}"/>
+    <workbookView xWindow="14820" yWindow="4500" windowWidth="41160" windowHeight="18980" xr2:uid="{5F9E506D-38E0-084A-B434-EE95D9C6630C}"/>
   </bookViews>
   <sheets>
     <sheet name="FreeDSP_INTEGRA_PANELBOARD" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FreeDSP_INTEGRA_PANELBOARD!$A$3:$E$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">FreeDSP_INTEGRA_PANELBOARD!$A$1:$E$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">FreeDSP_INTEGRA_PANELBOARD!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="88">
   <si>
     <t>Reference</t>
   </si>
@@ -47,9 +47,6 @@
     <t>0.1uF/50V</t>
   </si>
   <si>
-    <t>C14663</t>
-  </si>
-  <si>
     <t>Capacitor_THT:C_Disc_D4.3mm_W1.9mm_P5.00mm</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
     <t>C2</t>
   </si>
   <si>
-    <t>C28233</t>
-  </si>
-  <si>
     <t>C3</t>
   </si>
   <si>
@@ -71,30 +65,18 @@
     <t>10uF/25V</t>
   </si>
   <si>
-    <t>C45783</t>
-  </si>
-  <si>
     <t>Capacitor_SMD:C_0805_2012Metric</t>
   </si>
   <si>
     <t>D1,D2,D6,D7,D9</t>
   </si>
   <si>
-    <t>BAT43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C81598 </t>
-  </si>
-  <si>
     <t>Diode_THT:D_A-405_P7.62mm_Horizontal</t>
   </si>
   <si>
     <t>D3,D4,D5,D8</t>
   </si>
   <si>
-    <t>LED_RED</t>
-  </si>
-  <si>
     <t>LED_THT:LED_D3.0mm_FlatTop</t>
   </si>
   <si>
@@ -167,43 +149,16 @@
     <t>22k</t>
   </si>
   <si>
-    <t>C31850</t>
-  </si>
-  <si>
     <t>R5,R6,R7,R19,R20,R21</t>
   </si>
   <si>
     <t>10k</t>
   </si>
   <si>
-    <t>C25804</t>
-  </si>
-  <si>
-    <t>R9,R10,R11,R12,R13,R14,R15,R16</t>
-  </si>
-  <si>
-    <t>75R</t>
-  </si>
-  <si>
-    <t>C4275</t>
-  </si>
-  <si>
     <t>R17,R18</t>
   </si>
   <si>
     <t>0R</t>
-  </si>
-  <si>
-    <t>C21189</t>
-  </si>
-  <si>
-    <t>R22,R23,R24,R25</t>
-  </si>
-  <si>
-    <t>33R</t>
-  </si>
-  <si>
-    <t>C23140</t>
   </si>
   <si>
     <t>SW1</t>
@@ -276,14 +231,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>https://akizukidenshi.com/catalog/g/g113907/</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>https://akizukidenshi.com/catalog/g/g111577/</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>https://akizukidenshi.com/catalog/g/g100167/</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -308,24 +255,69 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>390R</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>1k</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>http://optoelectronics.liteon.com/upload/download/DS30-2001-093/LTC-4627JD.pdf
-https://akizukidenshi.com/catalog/g/g109968/</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>Display_7Segment:LTC-4627Jx (Anode Common)</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
     <t>Through-hole Lead Type Carbon Resistor 1/6W  (5mm pitch)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>47R</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>R9,R10,R11,R12,R13,R14,R15,R16,R22,R23,R24,R25</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>470R</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>JUMPER</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>LED_YELLOW</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>HAND</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>M3 Screw &amp; 10mm Spacer</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://akizukidenshi.com/catalog/g/g111639/</t>
+  </si>
+  <si>
+    <t>https://akizukidenshi.com/catalog/g/g113907/
+https://akizukidenshi.com/catalog/g/g116384/</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>BAT43
+1S4</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://akizukidenshi.com/catalog/g/g109968/
+http://optoelectronics.liteon.com/upload/download/DS30-2001-093/LTC-4627JD.pdf</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>NOP</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>MLCC 5mm pitch</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -521,7 +513,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -704,6 +696,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1007,7 +1005,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1026,11 +1024,11 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="42" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1040,6 +1038,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1420,10 +1421,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="63.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="84.7109375" customWidth="1"/>
@@ -1431,7 +1432,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="31">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1">
@@ -1459,411 +1460,398 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="E7" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="42">
+      <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>81</v>
+      <c r="E8" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="E11" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="D16" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="D17" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>93</v>
+      <c r="A18" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="336">
+      <c r="A22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="E24" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="42">
+      <c r="A25" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="105">
-      <c r="A23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="42">
-      <c r="A26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>91</v>
+      <c r="E26" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>80</v>
+        <v>64</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1873,15 +1861,14 @@
   </mergeCells>
   <phoneticPr fontId="18"/>
   <hyperlinks>
-    <hyperlink ref="E23" r:id="rId1" display="https://akizukidenshi.com/catalog/g/g106357/_x000a_https://ja.aliexpress.com/item/1005012129021462.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.2.4d053lvQ3lvQ8i&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40050.354490.0&amp;scm_id=1007.40050.354490.0&amp;scm-url=1007.40050.354490.0&amp;pvid=e0b7cc45-f1b5-4d73-a206-cf6449d124c2&amp;_t=gps-id%3ApcDetailTopMoreOtherSeller%2Cscm-url%3A1007.40050.354490.0%2Cpvid%3Ae0b7cc45-f1b5-4d73-a206-cf6449d124c2%2Ctpp_buckets%3A668%232846%238116%232002&amp;pdp_ext_f=%7B%22order%22%3A%22-1%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22sceneId%22%3A%2230050%22%2C%22fromPage%22%3A%22recommend%22%7D&amp;pdp_npi=6%40dis%21JPY%211009%21181%21%21%2143.04%217.75%21%402101529317777844403287573ea9cd%2112000057600170808%21rec%21JP%21230125749%21XZ%211%210%21n_tag%3A-29919%3Bd%3A29f7f230%3Bm03_new_user%3A-29895&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A%7Cx_object_id%3A1005012129021462%7C_p_origin_prod%3A" xr:uid="{9E4CCE21-269C-8949-84AF-F6FE150404A3}"/>
-    <hyperlink ref="E28" r:id="rId2" xr:uid="{0F99E362-A87D-1442-B7FA-93F2FE08B4CB}"/>
-    <hyperlink ref="E8" r:id="rId3" xr:uid="{699A241F-09C3-5749-B4B3-6CF791DB2B76}"/>
-    <hyperlink ref="E9" r:id="rId4" xr:uid="{4475A776-D1C6-C743-A7B4-F8EB9FB76A6D}"/>
-    <hyperlink ref="E11" r:id="rId5" xr:uid="{ADA0B455-8D90-6D4C-A12F-E27D97E1E262}"/>
-    <hyperlink ref="E24" r:id="rId6" xr:uid="{45439DD3-F871-734E-8F17-D537B287D44E}"/>
-    <hyperlink ref="E26" r:id="rId7" display="http://optoelectronics.liteon.com/upload/download/DS30-2001-093/LTC-4627JD.pdf" xr:uid="{A7E897EA-DA1A-7B43-8433-8D9AD92EA372}"/>
+    <hyperlink ref="E22" r:id="rId1" display="https://akizukidenshi.com/catalog/g/g106357/_x000a_https://ja.aliexpress.com/item/1005012129021462.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.2.4d053lvQ3lvQ8i&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40050.354490.0&amp;scm_id=1007.40050.354490.0&amp;scm-url=1007.40050.354490.0&amp;pvid=e0b7cc45-f1b5-4d73-a206-cf6449d124c2&amp;_t=gps-id%3ApcDetailTopMoreOtherSeller%2Cscm-url%3A1007.40050.354490.0%2Cpvid%3Ae0b7cc45-f1b5-4d73-a206-cf6449d124c2%2Ctpp_buckets%3A668%232846%238116%232002&amp;pdp_ext_f=%7B%22order%22%3A%22-1%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22sceneId%22%3A%2230050%22%2C%22fromPage%22%3A%22recommend%22%7D&amp;pdp_npi=6%40dis%21JPY%211009%21181%21%21%2143.04%217.75%21%402101529317777844403287573ea9cd%2112000057600170808%21rec%21JP%21230125749%21XZ%211%210%21n_tag%3A-29919%3Bd%3A29f7f230%3Bm03_new_user%3A-29895&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A%7Cx_object_id%3A1005012129021462%7C_p_origin_prod%3A" xr:uid="{9E4CCE21-269C-8949-84AF-F6FE150404A3}"/>
+    <hyperlink ref="E27" r:id="rId2" xr:uid="{0F99E362-A87D-1442-B7FA-93F2FE08B4CB}"/>
+    <hyperlink ref="E8" r:id="rId3" display="https://akizukidenshi.com/catalog/g/g113907/" xr:uid="{699A241F-09C3-5749-B4B3-6CF791DB2B76}"/>
+    <hyperlink ref="E11" r:id="rId4" xr:uid="{ADA0B455-8D90-6D4C-A12F-E27D97E1E262}"/>
+    <hyperlink ref="E23" r:id="rId5" xr:uid="{45439DD3-F871-734E-8F17-D537B287D44E}"/>
+    <hyperlink ref="E25" r:id="rId6" display="http://optoelectronics.liteon.com/upload/download/DS30-2001-093/LTC-4627JD.pdf" xr:uid="{A7E897EA-DA1A-7B43-8433-8D9AD92EA372}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="53" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>